--- a/Development/Common/GameData/Spawner.xlsx
+++ b/Development/Common/GameData/Spawner.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="38280" yWindow="5355" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Spawner" sheetId="1" state="visible" r:id="rId1"/>
@@ -557,7 +557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="21.25" customWidth="1" style="12" min="1" max="1"/>
@@ -569,7 +569,8 @@
     <col width="28.625" customWidth="1" style="3" min="7" max="7"/>
     <col width="36" customWidth="1" style="3" min="8" max="8"/>
     <col width="18.75" customWidth="1" style="3" min="9" max="9"/>
-    <col width="9" customWidth="1" style="3" min="10" max="16384"/>
+    <col width="9" customWidth="1" style="3" min="10" max="10"/>
+    <col width="9" customWidth="1" style="3" min="11" max="16384"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -840,7 +841,7 @@
         <v>4</v>
       </c>
       <c r="F9" t="n">
-        <v>20000</v>
+        <v>15000</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -894,7 +895,7 @@
         <v>4</v>
       </c>
       <c r="F11" t="n">
-        <v>20000</v>
+        <v>15000</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -921,7 +922,7 @@
         <v>4</v>
       </c>
       <c r="F12" t="n">
-        <v>18000</v>
+        <v>15000</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -948,7 +949,7 @@
         <v>4</v>
       </c>
       <c r="F13" t="n">
-        <v>25000</v>
+        <v>15000</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -975,7 +976,7 @@
         <v>4</v>
       </c>
       <c r="F14" t="n">
-        <v>25000</v>
+        <v>15000</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1002,7 +1003,7 @@
         <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>40000</v>
+        <v>15000</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1029,7 +1030,7 @@
         <v>1</v>
       </c>
       <c r="F16" t="n">
-        <v>45000</v>
+        <v>15000</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1038,6 +1039,33 @@
       </c>
       <c r="H16" t="n">
         <v>60</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="n">
+        <v>2101</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>레이드1 보스(아레나 중앙)</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>20</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" t="n">
+        <v>60000</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>PlayerProximity</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>50</v>
       </c>
     </row>
   </sheetData>
